--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.02836879432624113</v>
+        <v>0.02112676056338028</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0352112676056338</v>
+        <v>0.02112676056338028</v>
       </c>
       <c r="D2">
-        <v>0.9716312056737588</v>
+        <v>0.9788732394366197</v>
       </c>
       <c r="E2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.02112676056338028</v>
+        <v>0.007142857142857143</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -429,16 +429,16 @@
         <v>0.02112676056338028</v>
       </c>
       <c r="D2">
-        <v>0.9788732394366197</v>
+        <v>0.9928571428571429</v>
       </c>
       <c r="E2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
